--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487578_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487578_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>B. BAILLO HERNÁNDEZ</t>
+          <t>D. VAL GUTIERREZ</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.0045</v>
+        <v>2.7213</v>
       </c>
       <c r="E2" t="n">
-        <v>3.0198</v>
+        <v>1.5677</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.0153</v>
+        <v>1.1537</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9069</v>
+        <v>2.1045</v>
       </c>
       <c r="H2" t="n">
-        <v>1.0282</v>
+        <v>0.945</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.1213</v>
+        <v>1.1595</v>
       </c>
       <c r="J2" t="n">
-        <v>1.1758</v>
+        <v>3.1853</v>
       </c>
       <c r="K2" t="n">
-        <v>1.6807</v>
+        <v>1.3306</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.5049</v>
+        <v>1.8547</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.2688</v>
+        <v>-1.0808</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.6525</v>
+        <v>-0.3856</v>
       </c>
       <c r="O2" t="n">
-        <v>0.3837</v>
+        <v>-0.6952</v>
       </c>
       <c r="P2" t="n">
-        <v>1.5523</v>
+        <v>0.5821</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>-0.9702</v>
       </c>
       <c r="R2" t="n">
         <v>1.5523</v>
       </c>
       <c r="S2" t="n">
-        <v>0.4975</v>
+        <v>-0.9071</v>
       </c>
       <c r="T2" t="n">
-        <v>0.6202</v>
+        <v>-0.9295</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.1227</v>
+        <v>0.0225</v>
       </c>
       <c r="V2" t="n">
-        <v>0.0478</v>
+        <v>0.9418</v>
       </c>
       <c r="W2" t="n">
-        <v>1.2239</v>
+        <v>0.2821</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.1761</v>
+        <v>0.6597</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>D. VAL GUTIERREZ</t>
+          <t>B. BAILLO HERNÁNDEZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.8877</v>
+        <v>2.5824</v>
       </c>
       <c r="E3" t="n">
-        <v>1.407</v>
+        <v>2.3797</v>
       </c>
       <c r="F3" t="n">
-        <v>1.4807</v>
+        <v>0.2027</v>
       </c>
       <c r="G3" t="n">
-        <v>2.1045</v>
+        <v>0.9069</v>
       </c>
       <c r="H3" t="n">
-        <v>0.945</v>
+        <v>1.0282</v>
       </c>
       <c r="I3" t="n">
-        <v>1.1595</v>
+        <v>-0.1213</v>
       </c>
       <c r="J3" t="n">
-        <v>3.1853</v>
+        <v>1.1758</v>
       </c>
       <c r="K3" t="n">
-        <v>1.3306</v>
+        <v>1.6807</v>
       </c>
       <c r="L3" t="n">
-        <v>1.8547</v>
+        <v>-0.5049</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.0808</v>
+        <v>-0.2688</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.3856</v>
+        <v>-0.6525</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.6952</v>
+        <v>0.3837</v>
       </c>
       <c r="P3" t="n">
-        <v>0.5821</v>
+        <v>1.5523</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.9702</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
         <v>1.5523</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.7407</v>
+        <v>0.07539999999999999</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.0902</v>
+        <v>-0.0199</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3495</v>
+        <v>0.0954</v>
       </c>
       <c r="V3" t="n">
-        <v>0.9418</v>
+        <v>0.0478</v>
       </c>
       <c r="W3" t="n">
-        <v>0.2821</v>
+        <v>1.2239</v>
       </c>
       <c r="X3" t="n">
-        <v>0.6597</v>
+        <v>-1.1761</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.7040999999999999</v>
+        <v>0.8315</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3603</v>
+        <v>0.4604</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3438</v>
+        <v>0.3711</v>
       </c>
       <c r="G4" t="n">
         <v>0.7987</v>
@@ -766,13 +766,13 @@
         <v>0.7761</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.5886</v>
+        <v>-0.4612</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.4116</v>
+        <v>-0.3115</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.177</v>
+        <v>-0.1497</v>
       </c>
       <c r="V4" t="n">
         <v>-0.2821</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.0395</v>
+        <v>-0.6608000000000001</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.3631</v>
+        <v>-0.2024</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.6764</v>
+        <v>-0.4584</v>
       </c>
       <c r="G5" t="n">
         <v>0.8675</v>
@@ -844,13 +844,13 @@
         <v>0.9702</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.8607</v>
+        <v>-0.482</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.6057</v>
+        <v>-0.445</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.255</v>
+        <v>-0.037</v>
       </c>
       <c r="V5" t="n">
         <v>0.894</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>S. VAL GUTIERREZ</t>
+          <t>L. RODRIGUEZ SANCHEZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.8725</v>
+        <v>-1.3088</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.3734</v>
+        <v>0.7354000000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.4991</v>
+        <v>-2.0442</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.0163</v>
+        <v>-1.8898</v>
       </c>
       <c r="H6" t="n">
-        <v>0.131</v>
+        <v>-0.9499</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.1473</v>
+        <v>-0.9398</v>
       </c>
       <c r="J6" t="n">
-        <v>0.8496</v>
+        <v>0.3766</v>
       </c>
       <c r="K6" t="n">
-        <v>0.7456</v>
+        <v>-0.2018</v>
       </c>
       <c r="L6" t="n">
-        <v>0.104</v>
+        <v>0.5784</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.866</v>
+        <v>-2.2664</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.6146</v>
+        <v>-0.7481</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.2513</v>
+        <v>-1.5183</v>
       </c>
       <c r="P6" t="n">
-        <v>-1.5523</v>
+        <v>0.5821</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.9105</v>
+        <v>-0.9702</v>
       </c>
       <c r="R6" t="n">
-        <v>1.3582</v>
+        <v>1.5523</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.48</v>
+        <v>-1.5071</v>
       </c>
       <c r="T6" t="n">
-        <v>0.5114</v>
+        <v>-0.177</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.9913999999999999</v>
+        <v>-1.3301</v>
       </c>
       <c r="V6" t="n">
-        <v>1.1761</v>
+        <v>1.506</v>
       </c>
       <c r="W6" t="n">
-        <v>1.1761</v>
+        <v>1.506</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>L. RODRIGUEZ SANCHEZ</t>
+          <t>S. VAL GUTIERREZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.8995</v>
+        <v>-2.209</v>
       </c>
       <c r="E7" t="n">
-        <v>0.6353</v>
+        <v>-0.5736</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.5348</v>
+        <v>-1.6354</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.8898</v>
+        <v>-1.0163</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.9499</v>
+        <v>0.131</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.9398</v>
+        <v>-1.1473</v>
       </c>
       <c r="J7" t="n">
-        <v>0.3766</v>
+        <v>0.8496</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.2018</v>
+        <v>0.7456</v>
       </c>
       <c r="L7" t="n">
-        <v>0.5784</v>
+        <v>0.104</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.2664</v>
+        <v>-1.866</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.7481</v>
+        <v>-0.6146</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.5183</v>
+        <v>-1.2513</v>
       </c>
       <c r="P7" t="n">
-        <v>0.5821</v>
+        <v>-1.5523</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.9702</v>
+        <v>-2.9105</v>
       </c>
       <c r="R7" t="n">
-        <v>1.5523</v>
+        <v>1.3582</v>
       </c>
       <c r="S7" t="n">
-        <v>-2.0978</v>
+        <v>-0.8165</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.2771</v>
+        <v>0.3112</v>
       </c>
       <c r="U7" t="n">
-        <v>-1.8207</v>
+        <v>-1.1277</v>
       </c>
       <c r="V7" t="n">
-        <v>1.506</v>
+        <v>1.1761</v>
       </c>
       <c r="W7" t="n">
-        <v>1.506</v>
+        <v>1.1761</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-3.4375</v>
+        <v>-3.1311</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.7223000000000001</v>
+        <v>-0.3614</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.7152</v>
+        <v>-2.7698</v>
       </c>
       <c r="G8" t="n">
         <v>-4.2245</v>
@@ -1078,13 +1078,13 @@
         <v>1.3582</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.4562</v>
+        <v>-1.1499</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2894</v>
+        <v>0.07149999999999999</v>
       </c>
       <c r="U8" t="n">
-        <v>-1.1668</v>
+        <v>-1.2213</v>
       </c>
       <c r="V8" t="n">
         <v>2.8254</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-5.1867</v>
+        <v>-5.3596</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.3983</v>
+        <v>-3.5985</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.7884</v>
+        <v>-1.7611</v>
       </c>
       <c r="G9" t="n">
         <v>-2.0729</v>
@@ -1156,13 +1156,13 @@
         <v>0.9702</v>
       </c>
       <c r="S9" t="n">
-        <v>0.07870000000000001</v>
+        <v>-0.09420000000000001</v>
       </c>
       <c r="T9" t="n">
-        <v>0.8625</v>
+        <v>0.6623</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.7837</v>
+        <v>-0.7565</v>
       </c>
       <c r="V9" t="n">
         <v>-0.2821</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-8.408799999999999</v>
+        <v>-8.411199999999999</v>
       </c>
       <c r="E10" t="n">
-        <v>-5.7148</v>
+        <v>-5.2539</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.694</v>
+        <v>-3.1573</v>
       </c>
       <c r="G10" t="n">
         <v>-4.0992</v>
@@ -1234,13 +1234,13 @@
         <v>1.5523</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.0872</v>
+        <v>-1.0896</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4588</v>
+        <v>0.0022</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.6284999999999999</v>
+        <v>-1.0918</v>
       </c>
       <c r="V10" t="n">
         <v>-0.894</v>
@@ -1267,10 +1267,10 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-15.2482</v>
+        <v>-14.9453</v>
       </c>
       <c r="E11" t="n">
-        <v>-5.1495</v>
+        <v>-4.8466</v>
       </c>
       <c r="F11" t="n">
         <v>-10.0987</v>
@@ -1312,13 +1312,13 @@
         <v>11.6421</v>
       </c>
       <c r="S11" t="n">
-        <v>-6.735</v>
+        <v>-6.4322</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.1387</v>
+        <v>-0.8357</v>
       </c>
       <c r="U11" t="n">
-        <v>-5.596299999999999</v>
+        <v>-5.596200000000001</v>
       </c>
       <c r="V11" t="n">
         <v>5.9329</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>7.5302</v>
+        <v>8.3742</v>
       </c>
       <c r="E12" t="n">
-        <v>5.119</v>
+        <v>6.3202</v>
       </c>
       <c r="F12" t="n">
-        <v>2.4112</v>
+        <v>2.0541</v>
       </c>
       <c r="G12" t="n">
         <v>6.4765</v>
@@ -1390,13 +1390,13 @@
         <v>1.5523</v>
       </c>
       <c r="S12" t="n">
-        <v>0.4715</v>
+        <v>1.3156</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.6539</v>
+        <v>0.5473</v>
       </c>
       <c r="U12" t="n">
-        <v>1.1254</v>
+        <v>0.7683</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.3439</v>
+        <v>4.7988</v>
       </c>
       <c r="E13" t="n">
-        <v>1.4009</v>
+        <v>1.8013</v>
       </c>
       <c r="F13" t="n">
-        <v>2.943</v>
+        <v>2.9975</v>
       </c>
       <c r="G13" t="n">
         <v>1.8513</v>
@@ -1468,13 +1468,13 @@
         <v>2.3284</v>
       </c>
       <c r="S13" t="n">
-        <v>0.5702</v>
+        <v>1.0251</v>
       </c>
       <c r="T13" t="n">
-        <v>0.4991</v>
+        <v>0.8995</v>
       </c>
       <c r="U13" t="n">
-        <v>0.0711</v>
+        <v>0.1256</v>
       </c>
       <c r="V13" t="n">
         <v>0.5642</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.8698</v>
+        <v>4.1851</v>
       </c>
       <c r="E14" t="n">
-        <v>2.6713</v>
+        <v>2.7714</v>
       </c>
       <c r="F14" t="n">
-        <v>1.1985</v>
+        <v>1.4137</v>
       </c>
       <c r="G14" t="n">
         <v>2.015</v>
@@ -1546,13 +1546,13 @@
         <v>1.5523</v>
       </c>
       <c r="S14" t="n">
-        <v>0.613</v>
+        <v>0.9284</v>
       </c>
       <c r="T14" t="n">
-        <v>0.6202</v>
+        <v>0.7203000000000001</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.0072</v>
+        <v>0.2081</v>
       </c>
       <c r="V14" t="n">
         <v>0.6597</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.9113</v>
+        <v>3.4635</v>
       </c>
       <c r="E15" t="n">
-        <v>1.7494</v>
+        <v>2.2499</v>
       </c>
       <c r="F15" t="n">
-        <v>1.1619</v>
+        <v>1.2136</v>
       </c>
       <c r="G15" t="n">
         <v>0.9517</v>
@@ -1624,13 +1624,13 @@
         <v>2.7164</v>
       </c>
       <c r="S15" t="n">
-        <v>0.467</v>
+        <v>1.0192</v>
       </c>
       <c r="T15" t="n">
-        <v>0.1839</v>
+        <v>0.6844</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2831</v>
+        <v>0.3348</v>
       </c>
       <c r="V15" t="n">
         <v>-1.2239</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.3101</v>
+        <v>2.0248</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.3153</v>
+        <v>-0.8158</v>
       </c>
       <c r="F16" t="n">
-        <v>2.6254</v>
+        <v>2.8406</v>
       </c>
       <c r="G16" t="n">
         <v>1.644</v>
@@ -1702,13 +1702,13 @@
         <v>3.2985</v>
       </c>
       <c r="S16" t="n">
-        <v>1.2198</v>
+        <v>0.9345</v>
       </c>
       <c r="T16" t="n">
-        <v>1.5309</v>
+        <v>1.0304</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.3111</v>
+        <v>-0.0959</v>
       </c>
       <c r="V16" t="n">
         <v>-0.9418</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>D. VIERA LOPEZ</t>
+          <t>K. SKUTYELNIK</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.1878</v>
+        <v>-0.0259</v>
       </c>
       <c r="E17" t="n">
-        <v>1.2973</v>
+        <v>0.22</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.1095</v>
+        <v>-0.246</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.869</v>
+        <v>-0.2504</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.9186</v>
+        <v>-0.1458</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.9504</v>
+        <v>-0.1045</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.1154</v>
+        <v>1.4256</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.3995</v>
+        <v>1.38</v>
       </c>
       <c r="L17" t="n">
-        <v>0.2842</v>
+        <v>0.0456</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.7537</v>
+        <v>-1.676</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.5191</v>
+        <v>-1.5258</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.2346</v>
+        <v>-0.1502</v>
       </c>
       <c r="P17" t="n">
-        <v>0.5821</v>
+        <v>-0.9702</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.9702</v>
+        <v>-1.9403</v>
       </c>
       <c r="R17" t="n">
-        <v>1.5523</v>
+        <v>0.9702</v>
       </c>
       <c r="S17" t="n">
-        <v>4.2523</v>
+        <v>0.0185</v>
       </c>
       <c r="T17" t="n">
-        <v>3.7022</v>
+        <v>-0.4414</v>
       </c>
       <c r="U17" t="n">
-        <v>0.5501</v>
+        <v>0.4599</v>
       </c>
       <c r="V17" t="n">
-        <v>-2.7776</v>
+        <v>1.1761</v>
       </c>
       <c r="W17" t="n">
-        <v>-1.3194</v>
+        <v>1.1761</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.4582</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>K. SKUTYELNIK</t>
+          <t>J. LARREA IBARBURU</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1498</v>
+        <v>-1.2086</v>
       </c>
       <c r="E18" t="n">
-        <v>0.4202</v>
+        <v>-0.9864000000000001</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.2704</v>
+        <v>-0.2223</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.2504</v>
+        <v>-1.4148</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.1458</v>
+        <v>-2.8185</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.1045</v>
+        <v>1.4036</v>
       </c>
       <c r="J18" t="n">
-        <v>1.4256</v>
+        <v>-0.9344</v>
       </c>
       <c r="K18" t="n">
-        <v>1.38</v>
+        <v>-2.3604</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0456</v>
+        <v>1.4259</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.676</v>
+        <v>-0.4804</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.5258</v>
+        <v>-0.4581</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.1502</v>
+        <v>-0.0223</v>
       </c>
       <c r="P18" t="n">
+        <v>1.9403</v>
+      </c>
+      <c r="Q18" t="n">
         <v>-0.9702</v>
       </c>
-      <c r="Q18" t="n">
-        <v>-1.9403</v>
-      </c>
       <c r="R18" t="n">
-        <v>0.9702</v>
+        <v>2.9105</v>
       </c>
       <c r="S18" t="n">
-        <v>0.1943</v>
+        <v>0.4315</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.2412</v>
+        <v>0.6362</v>
       </c>
       <c r="U18" t="n">
-        <v>0.4354</v>
+        <v>-0.2047</v>
       </c>
       <c r="V18" t="n">
-        <v>1.1761</v>
+        <v>-2.1657</v>
       </c>
       <c r="W18" t="n">
-        <v>1.1761</v>
+        <v>0.2821</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-2.4477</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. LARREA IBARBURU</t>
+          <t>D. VIERA LOPEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.2759</v>
+        <v>-1.4289</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.4869</v>
+        <v>-0.5044999999999999</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.789</v>
+        <v>-0.9244</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.4148</v>
+        <v>-1.869</v>
       </c>
       <c r="H19" t="n">
-        <v>-2.8185</v>
+        <v>-0.9186</v>
       </c>
       <c r="I19" t="n">
-        <v>1.4036</v>
+        <v>-0.9504</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.9344</v>
+        <v>-0.1154</v>
       </c>
       <c r="K19" t="n">
-        <v>-2.3604</v>
+        <v>-0.3995</v>
       </c>
       <c r="L19" t="n">
-        <v>1.4259</v>
+        <v>0.2842</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.4804</v>
+        <v>-1.7537</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.4581</v>
+        <v>-0.5191</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.0223</v>
+        <v>-1.2346</v>
       </c>
       <c r="P19" t="n">
-        <v>1.9403</v>
+        <v>0.5821</v>
       </c>
       <c r="Q19" t="n">
         <v>-0.9702</v>
       </c>
       <c r="R19" t="n">
-        <v>2.9105</v>
+        <v>1.5523</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.6357</v>
+        <v>2.6357</v>
       </c>
       <c r="T19" t="n">
-        <v>0.1357</v>
+        <v>1.9005</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.7714</v>
+        <v>0.7352</v>
       </c>
       <c r="V19" t="n">
-        <v>-2.1657</v>
+        <v>-2.7776</v>
       </c>
       <c r="W19" t="n">
-        <v>0.2821</v>
+        <v>-1.3194</v>
       </c>
       <c r="X19" t="n">
-        <v>-2.4477</v>
+        <v>-1.4582</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.7788</v>
+        <v>-3.6002</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.7572</v>
+        <v>-0.9574</v>
       </c>
       <c r="F20" t="n">
-        <v>-3.0216</v>
+        <v>-2.6428</v>
       </c>
       <c r="G20" t="n">
         <v>-0.7792</v>
@@ -2014,13 +2014,13 @@
         <v>0.5821</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.4175</v>
+        <v>-0.2389</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.1806</v>
+        <v>-0.3808</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2369</v>
+        <v>0.1419</v>
       </c>
       <c r="V20" t="n">
         <v>-1.2239</v>
@@ -2047,19 +2047,19 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>15.2482</v>
+        <v>16.5828</v>
       </c>
       <c r="E21" t="n">
         <v>10.0987</v>
       </c>
       <c r="F21" t="n">
-        <v>5.149500000000002</v>
+        <v>6.484</v>
       </c>
       <c r="G21" t="n">
         <v>8.6251</v>
       </c>
       <c r="H21" t="n">
-        <v>0.4779000000000004</v>
+        <v>0.4779</v>
       </c>
       <c r="I21" t="n">
         <v>8.147400000000001</v>
@@ -2092,13 +2092,13 @@
         <v>17.463</v>
       </c>
       <c r="S21" t="n">
-        <v>6.7349</v>
+        <v>8.069599999999999</v>
       </c>
       <c r="T21" t="n">
-        <v>5.5963</v>
+        <v>5.5964</v>
       </c>
       <c r="U21" t="n">
-        <v>1.1385</v>
+        <v>2.4732</v>
       </c>
       <c r="V21" t="n">
         <v>-5.9329</v>
